--- a/budget/output/Фин.модель — Новое Колпино.xlsx
+++ b/budget/output/Фин.модель — Новое Колпино.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Текущий бюджет" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="+30% ФОТ" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="+40% ФОТ" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="+30% ФОТ → 20%" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="+40% ФОТ → 20%" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1646,7 +1646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1661,7 +1661,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Финансовая модель — Новое Колпино  |  Сценарий: ФОТ +30%</t>
+          <t>Финансовая модель — Новое Колпино  |  ФОТ +30%  →  цель ЧП 20%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
         <v>10175224</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>12702250.075</v>
+        <v>16552098.32278481</v>
       </c>
     </row>
     <row r="6">
@@ -2337,7 +2337,7 @@
         <v>1479208</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>1599542.574999999</v>
+        <v>5449390.822784809</v>
       </c>
     </row>
     <row r="31">
@@ -2353,7 +2353,7 @@
       <c r="F31" s="16" t="inlineStr"/>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>32.9%</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
         <v>296432</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>416766.5749999993</v>
+        <v>4266614.822784809</v>
       </c>
     </row>
     <row r="36">
@@ -2505,7 +2505,7 @@
         <v>470864</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>604869</v>
+        <v>788195</v>
       </c>
     </row>
     <row r="39">
@@ -2530,32 +2530,32 @@
         <v>638864</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>772869</v>
+        <v>956195</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>✅ ЧИСТАЯ ПРИБЫЛЬ</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n">
+      <c r="B40" s="8" t="n">
         <v>113831</v>
       </c>
-      <c r="C40" s="14" t="n">
+      <c r="C40" s="8" t="n">
         <v>-205421</v>
       </c>
-      <c r="D40" s="14" t="n">
+      <c r="D40" s="8" t="n">
         <v>-125421</v>
       </c>
-      <c r="E40" s="14" t="n">
+      <c r="E40" s="8" t="n">
         <v>-125421</v>
       </c>
-      <c r="F40" s="14" t="n">
+      <c r="F40" s="8" t="n">
         <v>-342432</v>
       </c>
-      <c r="G40" s="14" t="n">
-        <v>-356102</v>
+      <c r="G40" s="8" t="n">
+        <v>3310420</v>
       </c>
     </row>
     <row r="41">
@@ -2571,7 +2571,7 @@
       <c r="F41" s="16" t="inlineStr"/>
       <c r="G41" s="16" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -2619,12 +2619,12 @@
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>Требуемая выручка (новый контракт)</t>
+          <t>Цель: рент. чистой прибыли</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>12,702,250 ₽</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="C46" s="19" t="n"/>
@@ -2636,14 +2636,10 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>Прирост выручки</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>+2,527,026 ₽</t>
-        </is>
-      </c>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr"/>
       <c r="C47" s="19" t="n"/>
       <c r="D47" s="19" t="n"/>
       <c r="E47" s="19" t="n"/>
@@ -2653,12 +2649,12 @@
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>Прирост контракта, %</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="inlineStr">
-        <is>
-          <t>+24.8%</t>
+          <t>Требуемая выручка (новый контракт)</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>16,552,098 ₽</t>
         </is>
       </c>
       <c r="C48" s="19" t="n"/>
@@ -2670,12 +2666,12 @@
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>Требуемая МЕСЯЧНАЯ ставка</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t>3,175,563 ₽/мес</t>
+          <t>Прирост выручки</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>+6,376,874 ₽</t>
         </is>
       </c>
       <c r="C49" s="19" t="n"/>
@@ -2687,12 +2683,12 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>Текущая МЕСЯЧНАЯ ставка</t>
+          <t>Прирост контракта, %</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>2,543,806 ₽/мес</t>
+          <t>+62.7%</t>
         </is>
       </c>
       <c r="C50" s="19" t="n"/>
@@ -2704,19 +2700,96 @@
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t>Рентабельность чистой прибыли</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>-2.8%</t>
-        </is>
-      </c>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr"/>
       <c r="C51" s="19" t="n"/>
       <c r="D51" s="19" t="n"/>
       <c r="E51" s="19" t="n"/>
       <c r="F51" s="19" t="n"/>
       <c r="G51" s="19" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>Требуемая МЕСЯЧНАЯ ставка</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>4,138,025 ₽/мес</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="n"/>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="19" t="n"/>
+      <c r="G52" s="19" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Текущая МЕСЯЧНАЯ ставка</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>2,543,806 ₽/мес</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="n"/>
+      <c r="D53" s="19" t="n"/>
+      <c r="E53" s="19" t="n"/>
+      <c r="F53" s="19" t="n"/>
+      <c r="G53" s="19" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Прирост мес. ставки</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>+1,594,219 ₽/мес</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="19" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="inlineStr"/>
+      <c r="C55" s="19" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="19" t="n"/>
+      <c r="F55" s="19" t="n"/>
+      <c r="G55" s="19" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Рентабельность ЧП (сценарий)</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="19" t="n"/>
+      <c r="F56" s="19" t="n"/>
+      <c r="G56" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2733,7 +2806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2748,7 +2821,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Финансовая модель — Новое Колпино  |  Сценарий: ФОТ +40%</t>
+          <t>Финансовая модель — Новое Колпино  |  ФОТ +40%  →  цель ЧП 20%</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2920,7 @@
         <v>10175224</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>13544592.1</v>
+        <v>17618354.05063291</v>
       </c>
     </row>
     <row r="6">
@@ -3424,7 +3497,7 @@
         <v>1479208</v>
       </c>
       <c r="G30" s="8" t="n">
-        <v>1639654.1</v>
+        <v>5713416.050632913</v>
       </c>
     </row>
     <row r="31">
@@ -3440,7 +3513,7 @@
       <c r="F31" s="16" t="inlineStr"/>
       <c r="G31" s="16" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3602,7 @@
         <v>296432</v>
       </c>
       <c r="G35" s="8" t="n">
-        <v>456878.0999999996</v>
+        <v>4530640.050632913</v>
       </c>
     </row>
     <row r="36">
@@ -3592,7 +3665,7 @@
         <v>470864</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>644981</v>
+        <v>838969</v>
       </c>
     </row>
     <row r="39">
@@ -3617,32 +3690,32 @@
         <v>638864</v>
       </c>
       <c r="G39" s="8" t="n">
-        <v>812981</v>
+        <v>1006969</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>✅ ЧИСТАЯ ПРИБЫЛЬ</t>
         </is>
       </c>
-      <c r="B40" s="14" t="n">
+      <c r="B40" s="8" t="n">
         <v>113831</v>
       </c>
-      <c r="C40" s="14" t="n">
+      <c r="C40" s="8" t="n">
         <v>-205421</v>
       </c>
-      <c r="D40" s="14" t="n">
+      <c r="D40" s="8" t="n">
         <v>-125421</v>
       </c>
-      <c r="E40" s="14" t="n">
+      <c r="E40" s="8" t="n">
         <v>-125421</v>
       </c>
-      <c r="F40" s="14" t="n">
+      <c r="F40" s="8" t="n">
         <v>-342432</v>
       </c>
-      <c r="G40" s="14" t="n">
-        <v>-356102</v>
+      <c r="G40" s="8" t="n">
+        <v>3523671</v>
       </c>
     </row>
     <row r="41">
@@ -3658,7 +3731,7 @@
       <c r="F41" s="16" t="inlineStr"/>
       <c r="G41" s="16" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3779,12 @@
     <row r="46">
       <c r="A46" s="17" t="inlineStr">
         <is>
-          <t>Требуемая выручка (новый контракт)</t>
+          <t>Цель: рент. чистой прибыли</t>
         </is>
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>13,544,592 ₽</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="C46" s="19" t="n"/>
@@ -3723,14 +3796,10 @@
     <row r="47">
       <c r="A47" s="17" t="inlineStr">
         <is>
-          <t>Прирост выручки</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>+3,369,368 ₽</t>
-        </is>
-      </c>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr"/>
       <c r="C47" s="19" t="n"/>
       <c r="D47" s="19" t="n"/>
       <c r="E47" s="19" t="n"/>
@@ -3740,12 +3809,12 @@
     <row r="48">
       <c r="A48" s="17" t="inlineStr">
         <is>
-          <t>Прирост контракта, %</t>
-        </is>
-      </c>
-      <c r="B48" s="18" t="inlineStr">
-        <is>
-          <t>+33.1%</t>
+          <t>Требуемая выручка (новый контракт)</t>
+        </is>
+      </c>
+      <c r="B48" s="20" t="inlineStr">
+        <is>
+          <t>17,618,354 ₽</t>
         </is>
       </c>
       <c r="C48" s="19" t="n"/>
@@ -3757,12 +3826,12 @@
     <row r="49">
       <c r="A49" s="17" t="inlineStr">
         <is>
-          <t>Требуемая МЕСЯЧНАЯ ставка</t>
-        </is>
-      </c>
-      <c r="B49" s="20" t="inlineStr">
-        <is>
-          <t>3,386,148 ₽/мес</t>
+          <t>Прирост выручки</t>
+        </is>
+      </c>
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>+7,443,130 ₽</t>
         </is>
       </c>
       <c r="C49" s="19" t="n"/>
@@ -3774,12 +3843,12 @@
     <row r="50">
       <c r="A50" s="17" t="inlineStr">
         <is>
-          <t>Текущая МЕСЯЧНАЯ ставка</t>
+          <t>Прирост контракта, %</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>2,543,806 ₽/мес</t>
+          <t>+73.1%</t>
         </is>
       </c>
       <c r="C50" s="19" t="n"/>
@@ -3791,19 +3860,96 @@
     <row r="51">
       <c r="A51" s="17" t="inlineStr">
         <is>
-          <t>Рентабельность чистой прибыли</t>
-        </is>
-      </c>
-      <c r="B51" s="20" t="inlineStr">
-        <is>
-          <t>-2.6%</t>
-        </is>
-      </c>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr"/>
       <c r="C51" s="19" t="n"/>
       <c r="D51" s="19" t="n"/>
       <c r="E51" s="19" t="n"/>
       <c r="F51" s="19" t="n"/>
       <c r="G51" s="19" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
+        <is>
+          <t>Требуемая МЕСЯЧНАЯ ставка</t>
+        </is>
+      </c>
+      <c r="B52" s="20" t="inlineStr">
+        <is>
+          <t>4,404,589 ₽/мес</t>
+        </is>
+      </c>
+      <c r="C52" s="19" t="n"/>
+      <c r="D52" s="19" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="19" t="n"/>
+      <c r="G52" s="19" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Текущая МЕСЯЧНАЯ ставка</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>2,543,806 ₽/мес</t>
+        </is>
+      </c>
+      <c r="C53" s="19" t="n"/>
+      <c r="D53" s="19" t="n"/>
+      <c r="E53" s="19" t="n"/>
+      <c r="F53" s="19" t="n"/>
+      <c r="G53" s="19" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="17" t="inlineStr">
+        <is>
+          <t>Прирост мес. ставки</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>+1,860,783 ₽/мес</t>
+        </is>
+      </c>
+      <c r="C54" s="19" t="n"/>
+      <c r="D54" s="19" t="n"/>
+      <c r="E54" s="19" t="n"/>
+      <c r="F54" s="19" t="n"/>
+      <c r="G54" s="19" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="17" t="inlineStr">
+        <is>
+          <t>──────────────────────────────</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="inlineStr"/>
+      <c r="C55" s="19" t="n"/>
+      <c r="D55" s="19" t="n"/>
+      <c r="E55" s="19" t="n"/>
+      <c r="F55" s="19" t="n"/>
+      <c r="G55" s="19" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Рентабельность ЧП (сценарий)</t>
+        </is>
+      </c>
+      <c r="B56" s="20" t="inlineStr">
+        <is>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="C56" s="19" t="n"/>
+      <c r="D56" s="19" t="n"/>
+      <c r="E56" s="19" t="n"/>
+      <c r="F56" s="19" t="n"/>
+      <c r="G56" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
